--- a/Dataset/Dataset Produk.xlsx
+++ b/Dataset/Dataset Produk.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAGw\backend\Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9C4206-8D55-43FB-BB42-66BD450481F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E486EAF8-FF70-4553-99E8-4AE64AC7D1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Product" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4310" uniqueCount="1378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4350" uniqueCount="1378">
   <si>
     <t>Nama Produk</t>
   </si>
@@ -12667,14 +12667,150 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="324" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A324" s="48" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B324" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C324" s="64" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D324" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="E324" s="45"/>
+      <c r="F324" s="44" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A325" s="66" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B325" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C325" s="66" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D325" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="E325" s="45"/>
+      <c r="F325" s="43" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A326" s="66" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B326" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C326" s="66" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D326" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="E326" s="45"/>
+      <c r="F326" s="43" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A327" s="66" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B327" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C327" s="66" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D327" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="E327" s="45"/>
+      <c r="F327" s="43" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A328" s="66" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B328" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C328" s="66" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D328" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="E328" s="45"/>
+      <c r="F328" s="43" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A329" s="66" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B329" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C329" s="66" t="s">
+        <v>105</v>
+      </c>
+      <c r="D329" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="E329" s="45"/>
+      <c r="F329" s="43" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A330" s="66" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B330" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C330" s="66" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D330" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="E330" s="45"/>
+      <c r="F330" s="43" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A331" s="66" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B331" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C331" s="66" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D331" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="E331" s="45"/>
+      <c r="F331" s="43" t="s">
+        <v>1377</v>
+      </c>
+    </row>
     <row r="332" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="333" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="334" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
